--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486980_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486980_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4749</v>
+        <v>7.6981</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4119</v>
+        <v>5.5165</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0631</v>
+        <v>2.1816</v>
       </c>
       <c r="G2" t="n">
         <v>5.3493</v>
@@ -610,13 +610,13 @@
         <v>1.0267</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5602</v>
+        <v>-0.337</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1858</v>
+        <v>0.2904</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.746</v>
+        <v>-0.6274</v>
       </c>
       <c r="V2" t="n">
         <v>1.6591</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>D. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1517</v>
+        <v>5.7434</v>
       </c>
       <c r="E3" t="n">
-        <v>4.367</v>
+        <v>3.5963</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7847</v>
+        <v>2.1472</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0122</v>
+        <v>8.6137</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7312</v>
+        <v>4.6487</v>
       </c>
       <c r="I3" t="n">
-        <v>2.281</v>
+        <v>3.965</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8536</v>
+        <v>6.5761</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9466</v>
+        <v>4.1691</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9071</v>
+        <v>2.407</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1585</v>
+        <v>2.0375</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7846</v>
+        <v>0.4796</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6261</v>
+        <v>1.5579</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4107</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3266</v>
+        <v>-0.4677</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7905</v>
+        <v>0.2091</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5361</v>
+        <v>-0.6768</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8768</v>
+        <v>-0.3491</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3573</v>
+        <v>-0.1088</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4805</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. RIVAS PALMER</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1315</v>
+        <v>5.6706</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0733</v>
+        <v>4.708</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0583</v>
+        <v>0.9626</v>
       </c>
       <c r="G4" t="n">
-        <v>8.6137</v>
+        <v>5.0122</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6487</v>
+        <v>2.7312</v>
       </c>
       <c r="I4" t="n">
-        <v>3.965</v>
+        <v>2.281</v>
       </c>
       <c r="J4" t="n">
-        <v>6.5761</v>
+        <v>4.8536</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1691</v>
+        <v>1.9466</v>
       </c>
       <c r="L4" t="n">
-        <v>2.407</v>
+        <v>2.9071</v>
       </c>
       <c r="M4" t="n">
-        <v>2.0375</v>
+        <v>0.1585</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4796</v>
+        <v>0.7846</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5579</v>
+        <v>-0.6261</v>
       </c>
       <c r="P4" t="n">
+        <v>-0.4107</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-2.0534</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-3.0801</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0797</v>
+        <v>-0.8077</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3139</v>
+        <v>-0.4495</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7658</v>
+        <v>-0.3582</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3491</v>
+        <v>1.8768</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1088</v>
+        <v>2.3573</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2402</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.0732</v>
+        <v>5.5038</v>
       </c>
       <c r="E5" t="n">
-        <v>4.024</v>
+        <v>4.1286</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0491</v>
+        <v>1.3752</v>
       </c>
       <c r="G5" t="n">
         <v>4.1576</v>
@@ -844,13 +844,13 @@
         <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8093</v>
+        <v>-0.3787</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2517</v>
+        <v>0.3563</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.061</v>
+        <v>-0.735</v>
       </c>
       <c r="V5" t="n">
         <v>0.6982</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. CLEMENT AIGBOGUN</t>
+          <t>J. PALAMOS MOLINS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3303</v>
+        <v>3.5262</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4451</v>
+        <v>2.9786</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1147</v>
+        <v>0.5476</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5438</v>
+        <v>3.9969</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6622</v>
+        <v>5.0705</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1184</v>
+        <v>-1.0736</v>
       </c>
       <c r="J6" t="n">
-        <v>2.635</v>
+        <v>4.4277</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5695</v>
+        <v>4.4805</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0655</v>
+        <v>-0.0529</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9087</v>
+        <v>-0.4308</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0927</v>
+        <v>0.59</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1839</v>
+        <v>-1.0208</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6427</v>
+        <v>0.616</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
         <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3285</v>
+        <v>-0.8465</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0195</v>
+        <v>-0.4224</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.309</v>
+        <v>-0.4241</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5277</v>
+        <v>-0.2402</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8295</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3573</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PALAMOS MOLINS</t>
+          <t>K. CLEMENT AIGBOGUN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9935</v>
+        <v>3.3121</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7423</v>
+        <v>3.3676</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2512</v>
+        <v>-0.0555</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9969</v>
+        <v>3.5438</v>
       </c>
       <c r="H7" t="n">
-        <v>5.0705</v>
+        <v>3.6622</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0736</v>
+        <v>-0.1184</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4277</v>
+        <v>2.635</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4805</v>
+        <v>2.5695</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0529</v>
+        <v>0.0655</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4308</v>
+        <v>0.9087</v>
       </c>
       <c r="N7" t="n">
-        <v>0.59</v>
+        <v>1.0927</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0208</v>
+        <v>-0.1839</v>
       </c>
       <c r="P7" t="n">
-        <v>0.616</v>
+        <v>1.6427</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1.6427</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3792</v>
+        <v>-0.3466</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6587</v>
+        <v>-0.097</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7205</v>
+        <v>-0.2497</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2402</v>
+        <v>-1.5277</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.8295</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2402</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.827</v>
+        <v>3.0494</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2686</v>
+        <v>2.6096</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5583</v>
+        <v>0.4398</v>
       </c>
       <c r="G8" t="n">
         <v>1.4724</v>
@@ -1078,13 +1078,13 @@
         <v>1.8481</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7337</v>
+        <v>-0.5113</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6587</v>
+        <v>-0.3178</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.075</v>
+        <v>-0.1936</v>
       </c>
       <c r="V8" t="n">
         <v>0.2402</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>A. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9432</v>
+        <v>1.3334</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9597</v>
+        <v>0.485</v>
       </c>
       <c r="F9" t="n">
-        <v>3.903</v>
+        <v>0.8484</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5967</v>
+        <v>3.2182</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0387</v>
+        <v>1.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5579</v>
+        <v>2.0181</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5489000000000001</v>
+        <v>2.6121</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9436</v>
+        <v>0.6653</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3947</v>
+        <v>1.9469</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1456</v>
+        <v>0.6061</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9823</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1633</v>
+        <v>0.0713</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8481</v>
+        <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6607</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7514</v>
+        <v>-0.0737</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0907</v>
+        <v>-0.579</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2059</v>
+        <v>0.8981</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3866</v>
+        <v>-2.5602</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8193</v>
+        <v>3.4583</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7747000000000001</v>
+        <v>1.5967</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6325</v>
+        <v>0.0387</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1422</v>
+        <v>1.5579</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4138</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2954</v>
+        <v>-0.9436</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1184</v>
+        <v>0.3947</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3609</v>
+        <v>2.1456</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3371</v>
+        <v>0.9823</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0238</v>
+        <v>1.1633</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4107</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R10" t="n">
-        <v>0.616</v>
+        <v>1.8481</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9117</v>
+        <v>-0.3844</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.151</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9122</v>
+        <v>-0.5353</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0698</v>
+        <v>-0.1088</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.1088</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. RIVAS PALMER</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0789</v>
+        <v>0.104</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1712</v>
+        <v>-0.2411</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9077</v>
+        <v>0.3451</v>
       </c>
       <c r="G11" t="n">
-        <v>3.2182</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2</v>
+        <v>0.6325</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0181</v>
+        <v>0.1422</v>
       </c>
       <c r="J11" t="n">
-        <v>2.6121</v>
+        <v>0.4138</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6653</v>
+        <v>0.2954</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9469</v>
+        <v>0.1184</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6061</v>
+        <v>0.3609</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.3371</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0713</v>
+        <v>0.0238</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2321</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9073</v>
+        <v>0.8098</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3875</v>
+        <v>0.3719</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5197000000000001</v>
+        <v>0.4379</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.0698</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.0698</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3875</v>
+        <v>-2.3578</v>
       </c>
       <c r="E12" t="n">
         <v>-2.034</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3535</v>
+        <v>-0.3239</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3461</v>
@@ -1390,13 +1390,13 @@
         <v>0.2053</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1933</v>
+        <v>-0.1637</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1933</v>
+        <v>-0.1637</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82259999999999</v>
+        <v>34.4813</v>
       </c>
       <c r="E13" t="n">
-        <v>21.8963</v>
+        <v>22.5549</v>
       </c>
       <c r="F13" t="n">
-        <v>11.9265</v>
+        <v>11.9264</v>
       </c>
       <c r="G13" t="n">
-        <v>37.3894</v>
+        <v>37.38940000000001</v>
       </c>
       <c r="H13" t="n">
         <v>18.1161</v>
@@ -1450,16 +1450,16 @@
         <v>16.5872</v>
       </c>
       <c r="M13" t="n">
-        <v>8.731</v>
+        <v>8.730999999999998</v>
       </c>
       <c r="N13" t="n">
-        <v>6.045299999999999</v>
+        <v>6.0453</v>
       </c>
       <c r="O13" t="n">
-        <v>2.686</v>
+        <v>2.686000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.999999999976694e-05</v>
+        <v>-9.99999999995449e-05</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.3471</v>
@@ -1468,13 +1468,13 @@
         <v>13.3471</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.7454</v>
+        <v>-4.086500000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6403999999999999</v>
+        <v>0.01829999999999998</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.1049</v>
+        <v>-4.104900000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.1787</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.873</v>
+        <v>1.3538</v>
       </c>
       <c r="E14" t="n">
-        <v>6.9789</v>
+        <v>4.4684</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.1059</v>
+        <v>-3.1147</v>
       </c>
       <c r="G14" t="n">
         <v>-3.2579</v>
@@ -1546,13 +1546,13 @@
         <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4533</v>
+        <v>1.9341</v>
       </c>
       <c r="T14" t="n">
-        <v>4.3854</v>
+        <v>1.8749</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0679</v>
+        <v>0.0592</v>
       </c>
       <c r="V14" t="n">
         <v>0.8295</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>M. ISSOUF</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.8213</v>
+        <v>-1.6281</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5236</v>
+        <v>-0.8709</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.3449</v>
+        <v>-0.7573</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.1264</v>
+        <v>-0.1163</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5189</v>
+        <v>-0.1557</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.6074</v>
+        <v>0.0395</v>
       </c>
       <c r="J15" t="n">
-        <v>0.241</v>
+        <v>0.0784</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8988</v>
+        <v>0.0389</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6579</v>
+        <v>0.0395</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.3673</v>
+        <v>-0.1947</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4178</v>
+        <v>-0.1947</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.9495</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
+        <v>-0.4107</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-1.0267</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-2.0534</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>2.572</v>
+        <v>0.0775</v>
       </c>
       <c r="T15" t="n">
-        <v>2.336</v>
+        <v>0.0775</v>
       </c>
       <c r="U15" t="n">
-        <v>0.236</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ISSOUF</t>
+          <t>L. TVRDIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8373</v>
+        <v>-1.684</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0801</v>
+        <v>0.9264</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7573</v>
+        <v>-2.6103</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1163</v>
+        <v>-3.747</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1557</v>
+        <v>-3.0102</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0395</v>
+        <v>-0.7368</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0784</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0389</v>
+        <v>-0.9562</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0395</v>
+        <v>1.0257</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1947</v>
+        <v>-3.8165</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1947</v>
+        <v>-2.054</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-1.7626</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>0.616</v>
+        <v>2.2588</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1317</v>
+        <v>0.5907</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1317</v>
+        <v>0.4647</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X16" t="n">
         <v>-1.1786</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. TVRDIC</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.1101</v>
+        <v>-2.4464</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1941</v>
+        <v>-1.7817</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.3043</v>
+        <v>-0.6647</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.747</v>
+        <v>-6.3312</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.0102</v>
+        <v>-4.7552</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7368</v>
+        <v>-1.576</v>
       </c>
       <c r="J17" t="n">
-        <v>0.06950000000000001</v>
+        <v>-3.5723</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9562</v>
+        <v>-3.4799</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0257</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.8165</v>
+        <v>-2.7589</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.054</v>
+        <v>-1.2753</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7626</v>
+        <v>-1.4836</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2321</v>
+        <v>2.2588</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>2.2588</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8354</v>
+        <v>0.2072</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2675</v>
+        <v>-0.1088</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5679</v>
+        <v>0.3159</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2402</v>
+        <v>1.4189</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4189</v>
+        <v>1.8993</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1786</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.4049</v>
+        <v>-2.718</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2035</v>
+        <v>0.4241</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2014</v>
+        <v>-3.1421</v>
       </c>
       <c r="G18" t="n">
         <v>-4.0527</v>
@@ -1858,13 +1858,13 @@
         <v>0.4107</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0032</v>
+        <v>0.6837</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0968</v>
+        <v>0.7244</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="V18" t="n">
         <v>0.2402</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4122</v>
+        <v>-3.3154</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4093</v>
+        <v>-0.9409</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0029</v>
+        <v>-2.3745</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.3312</v>
+        <v>-3.1264</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.7552</v>
+        <v>-0.5189</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.576</v>
+        <v>-2.6074</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.5723</v>
+        <v>0.241</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.4799</v>
+        <v>0.8988</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.6579</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7589</v>
+        <v>-3.3673</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2753</v>
+        <v>-1.4178</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4836</v>
+        <v>-1.9495</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2588</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2588</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7587</v>
+        <v>1.0779</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7364000000000001</v>
+        <v>0.8716</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0223</v>
+        <v>0.2064</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4189</v>
+        <v>-0.2402</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8993</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4805</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>D. DE LA RUA DE AGUSTIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7393</v>
+        <v>-3.6536</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.0537</v>
+        <v>-2.5987</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3144</v>
+        <v>-1.0549</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8909</v>
+        <v>-2.6443</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9729</v>
+        <v>-3.8731</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9181</v>
+        <v>1.2288</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8418</v>
+        <v>-0.5452</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9207</v>
+        <v>-2.4001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0789</v>
+        <v>1.8549</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0492</v>
+        <v>-2.0991</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0522</v>
+        <v>-1.473</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.997</v>
+        <v>-0.6261</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.2588</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R20" t="n">
         <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4104</v>
+        <v>0.2227</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7827</v>
+        <v>-0.0001</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1932</v>
+        <v>0.2228</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. DE LA RUA DE AGUSTIN</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1453</v>
+        <v>-3.6993</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9125</v>
+        <v>-4.5307</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2327</v>
+        <v>0.8314</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6443</v>
+        <v>-1.8909</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.8731</v>
+        <v>-0.9729</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2288</v>
+        <v>-0.9181</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5452</v>
+        <v>-0.8418</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.4001</v>
+        <v>-0.9207</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8549</v>
+        <v>0.0789</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0991</v>
+        <v>-1.0492</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.473</v>
+        <v>-0.0522</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6261</v>
+        <v>-0.997</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.2321</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R21" t="n">
         <v>0.8214</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2689</v>
+        <v>0.4504</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3139</v>
+        <v>-0.2597</v>
       </c>
       <c r="U21" t="n">
-        <v>0.045</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.982</v>
+        <v>-4.2707</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4328</v>
+        <v>-1.119</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5493</v>
+        <v>-3.1518</v>
       </c>
       <c r="G22" t="n">
         <v>-6.0024</v>
@@ -2170,13 +2170,13 @@
         <v>2.0534</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0063</v>
+        <v>0.705</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2399</v>
+        <v>0.5537</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2463</v>
+        <v>0.1513</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1423</v>
+        <v>-5.0377</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3834</v>
+        <v>-2.2788</v>
       </c>
       <c r="F23" t="n">
         <v>-2.7589</v>
@@ -2248,10 +2248,10 @@
         <v>0.4107</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5733</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2672</v>
+        <v>0.3718</v>
       </c>
       <c r="U23" t="n">
         <v>0.3062</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1008</v>
+        <v>-5.3285</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1478</v>
+        <v>-3.6248</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.953</v>
+        <v>-1.7037</v>
       </c>
       <c r="G24" t="n">
         <v>-2.5394</v>
@@ -2326,13 +2326,13 @@
         <v>0.8214</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2595</v>
+        <v>-0.4872</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9881</v>
+        <v>-0.4651</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2715</v>
+        <v>-0.0222</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0698</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-33.8225</v>
+        <v>-32.4279</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.9265</v>
+        <v>-11.9266</v>
       </c>
       <c r="F25" t="n">
-        <v>-21.8962</v>
+        <v>-20.5015</v>
       </c>
       <c r="G25" t="n">
         <v>-37.3892</v>
@@ -2377,7 +2377,7 @@
         <v>-19.273</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.731300000000001</v>
+        <v>-8.731299999999999</v>
       </c>
       <c r="K25" t="n">
         <v>-6.045300000000001</v>
@@ -2395,7 +2395,7 @@
         <v>-16.5872</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.3471</v>
@@ -2404,13 +2404,13 @@
         <v>13.3474</v>
       </c>
       <c r="S25" t="n">
-        <v>4.745299999999999</v>
+        <v>6.139900000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>4.104999999999999</v>
+        <v>4.104900000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6403999999999999</v>
+        <v>2.0351</v>
       </c>
       <c r="V25" t="n">
         <v>-1.1787</v>
